--- a/database/seeders/excel/user.xlsx
+++ b/database/seeders/excel/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\mlti\database\seeders\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2C16E6-C4D0-4005-BB14-A55721ACE13C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1994622C-7B3A-42C8-9543-089DD4D8F889}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="221">
   <si>
     <t>nip_lama</t>
   </si>
@@ -667,6 +667,27 @@
   </si>
   <si>
     <t>id_ruang</t>
+  </si>
+  <si>
+    <t>is_umum</t>
+  </si>
+  <si>
+    <t>id_satker</t>
+  </si>
+  <si>
+    <t>Bari Rizki Pratama S.Tr.Stat.</t>
+  </si>
+  <si>
+    <t>Statistisi Ahli Utama</t>
+  </si>
+  <si>
+    <t>Baginda Sinaga S.Tr.Stat.</t>
+  </si>
+  <si>
+    <t>200310082026031002</t>
+  </si>
+  <si>
+    <t>199901142023021001</t>
   </si>
 </sst>
 </file>
@@ -702,8 +723,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -984,14 +1006,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1013,8 +1036,14 @@
       <c r="G1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>340014249</v>
       </c>
@@ -1036,8 +1065,14 @@
       <c r="G2">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>340014611</v>
       </c>
@@ -1059,8 +1094,14 @@
       <c r="G3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>340014682</v>
       </c>
@@ -1082,8 +1123,14 @@
       <c r="G4">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>340016477</v>
       </c>
@@ -1105,8 +1152,14 @@
       <c r="G5">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>340050052</v>
       </c>
@@ -1128,8 +1181,14 @@
       <c r="G6">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>340016847</v>
       </c>
@@ -1151,8 +1210,14 @@
       <c r="G7">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>340058230</v>
       </c>
@@ -1174,8 +1239,14 @@
       <c r="G8">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>340018098</v>
       </c>
@@ -1197,8 +1268,14 @@
       <c r="G9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>340055841</v>
       </c>
@@ -1220,8 +1297,14 @@
       <c r="G10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>340054647</v>
       </c>
@@ -1243,8 +1326,14 @@
       <c r="G11">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>340054663</v>
       </c>
@@ -1266,8 +1355,14 @@
       <c r="G12">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>340057887</v>
       </c>
@@ -1289,8 +1384,14 @@
       <c r="G13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>340018099</v>
       </c>
@@ -1312,8 +1413,14 @@
       <c r="G14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>340018936</v>
       </c>
@@ -1335,8 +1442,14 @@
       <c r="G15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>340063668</v>
       </c>
@@ -1358,8 +1471,14 @@
       <c r="G16">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>340063944</v>
       </c>
@@ -1381,8 +1500,14 @@
       <c r="G17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>340013114</v>
       </c>
@@ -1404,8 +1529,14 @@
       <c r="G18">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>340017517</v>
       </c>
@@ -1427,8 +1558,14 @@
       <c r="G19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>340054652</v>
       </c>
@@ -1450,8 +1587,14 @@
       <c r="G20">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>340061101</v>
       </c>
@@ -1473,8 +1616,14 @@
       <c r="G21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>340051219</v>
       </c>
@@ -1496,8 +1645,14 @@
       <c r="G22">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>340062133</v>
       </c>
@@ -1519,8 +1674,14 @@
       <c r="G23">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>340016846</v>
       </c>
@@ -1542,8 +1703,14 @@
       <c r="G24">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>340054662</v>
       </c>
@@ -1565,8 +1732,14 @@
       <c r="G25">
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>340014688</v>
       </c>
@@ -1588,8 +1761,14 @@
       <c r="G26">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>340017519</v>
       </c>
@@ -1611,8 +1790,14 @@
       <c r="G27">
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>340063917</v>
       </c>
@@ -1634,8 +1819,14 @@
       <c r="G28">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>340062122</v>
       </c>
@@ -1657,8 +1848,14 @@
       <c r="G29">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>340013729</v>
       </c>
@@ -1680,8 +1877,14 @@
       <c r="G30">
         <v>5</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>340056007</v>
       </c>
@@ -1703,8 +1906,14 @@
       <c r="G31">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>340061235</v>
       </c>
@@ -1726,8 +1935,14 @@
       <c r="G32">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>340063997</v>
       </c>
@@ -1749,8 +1964,14 @@
       <c r="G33">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>340065022</v>
       </c>
@@ -1772,8 +1993,14 @@
       <c r="G34">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>340065028</v>
       </c>
@@ -1795,8 +2022,14 @@
       <c r="G35">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>340065155</v>
       </c>
@@ -1818,8 +2051,14 @@
       <c r="G36">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>340065934</v>
       </c>
@@ -1841,8 +2080,14 @@
       <c r="G37">
         <v>12</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>340065949</v>
       </c>
@@ -1864,8 +2109,14 @@
       <c r="G38">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>340016277</v>
       </c>
@@ -1887,8 +2138,14 @@
       <c r="G39">
         <v>3</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>340016976</v>
       </c>
@@ -1910,8 +2167,14 @@
       <c r="G40">
         <v>3</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>340015539</v>
       </c>
@@ -1933,8 +2196,14 @@
       <c r="G41">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>340020005</v>
       </c>
@@ -1956,8 +2225,14 @@
       <c r="G42">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>340016170</v>
       </c>
@@ -1979,8 +2254,14 @@
       <c r="G43">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>340015872</v>
       </c>
@@ -2002,8 +2283,14 @@
       <c r="G44">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>340057209</v>
       </c>
@@ -2025,8 +2312,14 @@
       <c r="G45">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>340054168</v>
       </c>
@@ -2048,8 +2341,14 @@
       <c r="G46">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>340057667</v>
       </c>
@@ -2071,8 +2370,14 @@
       <c r="G47">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>340016191</v>
       </c>
@@ -2094,8 +2399,14 @@
       <c r="G48">
         <v>14</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>340016060</v>
       </c>
@@ -2117,8 +2428,14 @@
       <c r="G49">
         <v>14</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>340053548</v>
       </c>
@@ -2140,8 +2457,14 @@
       <c r="G50">
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>340017520</v>
       </c>
@@ -2163,8 +2486,14 @@
       <c r="G51">
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>340054653</v>
       </c>
@@ -2186,8 +2515,14 @@
       <c r="G52">
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>340058851</v>
       </c>
@@ -2209,8 +2544,14 @@
       <c r="G53">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>340018514</v>
       </c>
@@ -2232,8 +2573,14 @@
       <c r="G54">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>340060068</v>
       </c>
@@ -2255,8 +2602,14 @@
       <c r="G55">
         <v>14</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>340015731</v>
       </c>
@@ -2278,8 +2631,14 @@
       <c r="G56">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>340054174</v>
       </c>
@@ -2301,8 +2660,14 @@
       <c r="G57">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>340016971</v>
       </c>
@@ -2324,8 +2689,14 @@
       <c r="G58">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>340019122</v>
       </c>
@@ -2347,8 +2718,14 @@
       <c r="G59">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>340059155</v>
       </c>
@@ -2370,8 +2747,14 @@
       <c r="G60">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>340056947</v>
       </c>
@@ -2393,8 +2776,14 @@
       <c r="G61">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>340055852</v>
       </c>
@@ -2416,8 +2805,14 @@
       <c r="G62">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>340013506</v>
       </c>
@@ -2439,8 +2834,14 @@
       <c r="G63">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>340062195</v>
       </c>
@@ -2462,8 +2863,14 @@
       <c r="G64">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>340016973</v>
       </c>
@@ -2485,8 +2892,14 @@
       <c r="G65">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>340016187</v>
       </c>
@@ -2508,8 +2921,14 @@
       <c r="G66">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>340050143</v>
       </c>
@@ -2531,8 +2950,14 @@
       <c r="G67">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>340016574</v>
       </c>
@@ -2554,8 +2979,14 @@
       <c r="G68">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>340054175</v>
       </c>
@@ -2577,8 +3008,14 @@
       <c r="G69">
         <v>2</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>340060289</v>
       </c>
@@ -2600,8 +3037,14 @@
       <c r="G70">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>340058939</v>
       </c>
@@ -2623,8 +3066,14 @@
       <c r="G71">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>340056458</v>
       </c>
@@ -2646,8 +3095,14 @@
       <c r="G72">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>340059165</v>
       </c>
@@ -2669,8 +3124,14 @@
       <c r="G73">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>340013013</v>
       </c>
@@ -2692,8 +3153,14 @@
       <c r="G74">
         <v>8</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>340016975</v>
       </c>
@@ -2715,8 +3182,14 @@
       <c r="G75">
         <v>9</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>340055712</v>
       </c>
@@ -2738,8 +3211,14 @@
       <c r="G76">
         <v>8</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>340053273</v>
       </c>
@@ -2761,8 +3240,14 @@
       <c r="G77">
         <v>9</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>340056760</v>
       </c>
@@ -2784,8 +3269,14 @@
       <c r="G78">
         <v>9</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>340060080</v>
       </c>
@@ -2807,8 +3298,14 @@
       <c r="G79">
         <v>8</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>340058485</v>
       </c>
@@ -2830,8 +3327,14 @@
       <c r="G80">
         <v>8</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>340059630</v>
       </c>
@@ -2853,8 +3356,14 @@
       <c r="G81">
         <v>9</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>340057694</v>
       </c>
@@ -2876,8 +3385,14 @@
       <c r="G82">
         <v>8</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>340066553</v>
       </c>
@@ -2899,8 +3414,14 @@
       <c r="G83">
         <v>8</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>340061727</v>
       </c>
@@ -2922,8 +3443,14 @@
       <c r="G84">
         <v>17</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>340054170</v>
       </c>
@@ -2945,8 +3472,73 @@
       <c r="G85">
         <v>8</v>
       </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>340061716</v>
+      </c>
+      <c r="B86" t="s">
+        <v>216</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D86">
+        <v>12</v>
+      </c>
+      <c r="E86" t="s">
+        <v>217</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>98</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>340066157</v>
+      </c>
+      <c r="B87" t="s">
+        <v>218</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D87">
+        <v>12</v>
+      </c>
+      <c r="E87" t="s">
+        <v>206</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>98</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>1505</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>